--- a/samples/talentra/talentra-step04-d4.xlsx
+++ b/samples/talentra/talentra-step04-d4.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="143">
   <si>
     <t>How to fill in this scorecard</t>
   </si>
@@ -34,10 +34,13 @@
     <t xml:space="preserve">  id, version, judges are required. "judges" must start with D1 (a schema design) or D3 (an output document).</t>
   </si>
   <si>
-    <t xml:space="preserve">  frozen must be yes. A scorecard that is not frozen is refused, so the target cannot move mid-evaluation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  accept and refine are the green and amber thresholds (default 90 and 75). approval says who approved it; if it says "pending" or "draft", every report is marked provisional.</t>
+    <t xml:space="preserve">  frozen is optional: the app freezes every scorecard by its hash when work is submitted, so the target cannot move mid-evaluation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  accept and refine are the green and amber thresholds (default 90 and 75). approval (optional) is shown in the report header as where the scorecard came from.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  unmeasured (optional) = skip (default: a question the file holds nothing for is left out of the score) or zero (it counts as 0).</t>
   </si>
   <si>
     <t xml:space="preserve">  Format the version cell as Text, or Excel turns 1.0 into 1.</t>
@@ -61,7 +64,10 @@
     <t xml:space="preserve">  Weight = importance (any positive number; they need not add to 100). Critical = yes means it must score 4 or more or the verdict cannot be green.</t>
   </si>
   <si>
-    <t xml:space="preserve">  Measured by = code (counted exactly), raters (the AI examiners score 0-5 against your anchors) or human (only a person can supply it).</t>
+    <t xml:space="preserve">  Measured by = code (counted exactly) or raters (the AI examiners score 0-5 against your anchors). Nothing waits for a person:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        human is still accepted, and such a row is scored by the examiners from what the file shows (standard anchors if none are given).</t>
   </si>
   <si>
     <t xml:space="preserve">  raters: fill all six Anchor columns, saying what a 0, 1, 2, 3, 4 and 5 mean.</t>
@@ -79,9 +85,6 @@
     <t xml:space="preserve">        strict = 1:5, 0.97:4, 0.9:3, 0.75:2, 0.01:1     exact = 1:5, 0.01:1 (one mistake fails it)</t>
   </si>
   <si>
-    <t xml:space="preserve">  human: fill Needs, saying what the person must provide (for example a scored author interview).</t>
-  </si>
-  <si>
     <t xml:space="preserve">  Fix = what to do when a code check fails. Return to = which stage the author goes back to (Discover, Define, Generate, Analyse, Validate, Refine).</t>
   </si>
   <si>
@@ -133,7 +136,7 @@
     <t>approval</t>
   </si>
   <si>
-    <t>Draft by the assistant, pending mentor approval</t>
+    <t>Sample scorecard for the Talentra workbook, used as it is</t>
   </si>
   <si>
     <t>accept</t>
@@ -229,6 +232,9 @@
     <t>Return to</t>
   </si>
   <si>
+    <t>Reads</t>
+  </si>
+  <si>
     <t>O01</t>
   </si>
   <si>
@@ -415,7 +421,25 @@
     <t>Lead sign-off</t>
   </si>
   <si>
-    <t>human</t>
+    <t>The lead confirms that the proposed NFRs are approved. Proposed targets are not decisions until a person approves them. Score only what the file itself shows for this. If the file holds no evidence for it at all, mark it not measurable.</t>
+  </si>
+  <si>
+    <t>Every item meets it, with nothing missing.</t>
+  </si>
+  <si>
+    <t>Nearly all items meet it, with one minor gap.</t>
+  </si>
+  <si>
+    <t>Most items meet it, with clear gaps left.</t>
+  </si>
+  <si>
+    <t>About half of the items meet it, or there are serious gaps.</t>
+  </si>
+  <si>
+    <t>A few items meet it; most do not.</t>
+  </si>
+  <si>
+    <t>None of what the question asks for is in the file.</t>
   </si>
   <si>
     <t>The lead confirms that the proposed NFRs are approved. Proposed targets are not decisions until a person approves them.</t>
@@ -818,7 +842,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A28"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="150" customWidth="1"/>
@@ -876,16 +900,16 @@
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
     </row>
@@ -901,16 +925,16 @@
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
         <v>14</v>
       </c>
     </row>
@@ -956,12 +980,17 @@
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>23</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -981,71 +1010,71 @@
   <sheetData>
     <row r="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B9">
         <v>90</v>
@@ -1053,7 +1082,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B10">
         <v>75</v>
@@ -1078,44 +1107,44 @@
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B2">
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B3">
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="4:4" x14ac:dyDescent="0.25"/>
@@ -1332,7 +1361,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S201"/>
+  <dimension ref="A1:T201"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1345,73 +1374,77 @@
     <col min="16" max="16" width="26" customWidth="1"/>
     <col min="17" max="18" width="40" customWidth="1"/>
     <col min="19" max="19" width="12" customWidth="1"/>
+    <col min="20" max="20" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="R1" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C2" s="5">
         <v>6</v>
@@ -1420,7 +1453,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>1</v>
@@ -1447,16 +1480,16 @@
         <v>1</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="R2" s="5" t="s">
         <v>1</v>
@@ -1464,13 +1497,16 @@
       <c r="S2" s="5" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T2" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C3" s="5">
         <v>4</v>
@@ -1479,7 +1515,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>1</v>
@@ -1506,16 +1542,16 @@
         <v>1</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="R3" s="5" t="s">
         <v>1</v>
@@ -1523,13 +1559,16 @@
       <c r="S3" s="5" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T3" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C4" s="5">
         <v>4</v>
@@ -1538,7 +1577,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>1</v>
@@ -1565,16 +1604,16 @@
         <v>1</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O4" s="5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="R4" s="5" t="s">
         <v>1</v>
@@ -1582,25 +1621,28 @@
       <c r="S4" s="5" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T4" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C5" s="5">
         <v>10</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>1</v>
@@ -1624,16 +1666,16 @@
         <v>1</v>
       </c>
       <c r="N5" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="O5" s="5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="P5" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="Q5" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="R5" s="5" t="s">
         <v>1</v>
@@ -1641,22 +1683,25 @@
       <c r="S5" s="5" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T5" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C6" s="5">
         <v>10</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>1</v>
@@ -1683,16 +1728,16 @@
         <v>1</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="R6" s="5" t="s">
         <v>1</v>
@@ -1700,13 +1745,16 @@
       <c r="S6" s="5" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T6" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C7" s="5">
         <v>6</v>
@@ -1715,10 +1763,10 @@
         <v>1</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>1</v>
@@ -1742,16 +1790,16 @@
         <v>1</v>
       </c>
       <c r="N7" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="O7" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="P7" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="Q7" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R7" s="5" t="s">
         <v>1</v>
@@ -1759,13 +1807,16 @@
       <c r="S7" s="5" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T7" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C8" s="5">
         <v>18</v>
@@ -1774,31 +1825,31 @@
         <v>1</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>1</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="N8" s="5" t="s">
         <v>1</v>
@@ -1818,13 +1869,16 @@
       <c r="S8" s="5" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T8" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C9" s="5">
         <v>14</v>
@@ -1833,31 +1887,31 @@
         <v>1</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>1</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M9" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="N9" s="5" t="s">
         <v>1</v>
@@ -1877,46 +1931,49 @@
       <c r="S9" s="5" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T9" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C10" s="5">
         <v>18</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>1</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="M10" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="N10" s="5" t="s">
         <v>1</v>
@@ -1934,48 +1991,51 @@
         <v>1</v>
       </c>
       <c r="S10" s="5" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+      <c r="T10" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C11" s="5">
         <v>10</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>1</v>
+        <v>135</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>1</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>1</v>
+        <v>136</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>1</v>
+        <v>137</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>1</v>
+        <v>138</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>1</v>
+        <v>139</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>1</v>
+        <v>140</v>
       </c>
       <c r="M11" s="5" t="s">
-        <v>1</v>
+        <v>141</v>
       </c>
       <c r="N11" s="5" t="s">
         <v>1</v>
@@ -1990,9 +2050,12 @@
         <v>1</v>
       </c>
       <c r="R11" s="5" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="S11" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="T11" s="5" t="s">
         <v>1</v>
       </c>
     </row>
